--- a/ksoft_old/docs/records/Sales_Repres_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Repres_Records.xlsx
@@ -1595,13 +1595,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67D0F4B4-87CD-4B10-B270-43657641090E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C456CBD6-AD87-4943-80FD-02159F5D5B4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FD8B451-2B59-480D-BD4E-275393A5892C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850DB548-38C8-4199-A51D-8F785921F11D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9BCCCFC-D201-4BF1-9139-E619B967BEDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2BA8803-C374-4157-B54A-7E9F60A0AF14}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Repres_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Repres_Records.xlsx
@@ -1595,13 +1595,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C456CBD6-AD87-4943-80FD-02159F5D5B4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AB0778B-C5C5-4E92-BD2C-9DB3BAED04A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850DB548-38C8-4199-A51D-8F785921F11D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E547BE7B-669F-41B3-B63D-D8079EC55FCF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2BA8803-C374-4157-B54A-7E9F60A0AF14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D72C88-382F-4EC7-BEBA-0C39BA7644D4}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Repres_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Repres_Records.xlsx
@@ -1595,13 +1595,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AB0778B-C5C5-4E92-BD2C-9DB3BAED04A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67D0F4B4-87CD-4B10-B270-43657641090E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E547BE7B-669F-41B3-B63D-D8079EC55FCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FD8B451-2B59-480D-BD4E-275393A5892C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D72C88-382F-4EC7-BEBA-0C39BA7644D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9BCCCFC-D201-4BF1-9139-E619B967BEDD}"/>
 </file>